--- a/AAII_Financials/Quarterly/BN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
   <si>
     <t>BN</t>
   </si>
@@ -656,311 +656,323 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="25" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="26" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>20129000</v>
+      </c>
+      <c r="E8" s="3">
         <v>19919000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>21184000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>19460000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>18550000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>18463000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>20460000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>20807000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>23875000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>23593000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>24947000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>25250000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>24069000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>23726000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>24213000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>23418000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>23256000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>21882000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>21787000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>19248000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>18286000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>16410000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>17088000</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>14939000</v>
+      </c>
+      <c r="E9" s="3">
         <v>14138000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>10896000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>14632000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>13915000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>13450000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>10661000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>15344000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>19152000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>19046000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>16994000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>21088000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>19906000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>19820000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>20207000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>19768000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>19841000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>18695000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>16631000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>14751000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>13994000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>12187000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>12859000</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>5190000</v>
+      </c>
+      <c r="E10" s="3">
         <v>5781000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>10288000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4828000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4635000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5013000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>9799000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>5463000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4723000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4547000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>7953000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4162000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4163000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3906000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4006000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>3650000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>3415000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3187000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>5156000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>4497000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>4292000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>4223000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>4229000</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -986,8 +998,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1057,8 +1070,11 @@
       <c r="Y12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1128,53 +1144,56 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-38000</v>
+      </c>
+      <c r="E14" s="3">
         <v>187000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>782000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-655000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>75000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-199000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1924000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-978000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>194000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-682000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-3032000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>608000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-1546000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-542000</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
@@ -1199,52 +1218,55 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2711000</v>
+      </c>
+      <c r="E15" s="3">
         <v>2631000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2699000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2691000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2534000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2455000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2417000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2410000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2435000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2475000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2427000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2246000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2214000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>2188000</v>
-      </c>
-      <c r="Q15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="R15" s="3" t="s">
         <v>8</v>
@@ -1255,23 +1277,26 @@
       <c r="T15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U15" s="3">
+      <c r="U15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V15" s="3">
         <v>1739000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>1617000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>1571000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>1510000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>1536000</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1294,150 +1319,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>14961000</v>
+      </c>
+      <c r="E17" s="3">
         <v>14158000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>14998000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>14650000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>13935000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>13468000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>14414000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>15364000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>19171000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>19063000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>20611000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>21104000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>19929000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>19834000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>24074000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>22177000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>21640000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>18214000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>17810000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>15809000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>15310000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>12090000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>15030000</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>5168000</v>
+      </c>
+      <c r="E18" s="3">
         <v>5761000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>6186000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>4810000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>4615000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>4995000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>6046000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>5443000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>4704000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>4530000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4336000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>4146000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>4140000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3892000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>139000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1241000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1616000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3668000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>3977000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>3439000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2976000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>4320000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2058000</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1463,53 +1495,54 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-310000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-217000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-763000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>363000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-902000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>435000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-217000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>433000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>315000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>284000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>102000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-819000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>123000</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
@@ -1534,124 +1567,130 @@
       <c r="Y20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>8189000</v>
+      </c>
+      <c r="E21" s="3">
         <v>8609000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>9648000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>7138000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>8051000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>7015000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>8680000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>7420000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>6824000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>6721000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>6661000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>7211000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>6353000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>5957000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2128000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>3238000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>3502000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>5479000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>5716000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>5056000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>4547000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>5830000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>3594000</v>
       </c>
     </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>4477000</v>
+      </c>
+      <c r="E22" s="3">
         <v>4351000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>4372000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>4314000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>4253000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>4161000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>3979000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>4332000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>4176000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>4128000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>4045000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>4081000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>3764000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>3613000</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
@@ -1676,150 +1715,159 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1039000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1440000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1795000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>788000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1189000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>598000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>360000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1656000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>19000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>800000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3221000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>276000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1921000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>698000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>139000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1241000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1616000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>3668000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>3977000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>3439000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2976000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>4320000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2058000</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>336000</v>
+      </c>
+      <c r="E24" s="3">
         <v>398000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>114000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>504000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>134000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>383000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>259000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>138000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>304000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>281000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>87000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>241000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>409000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>274000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>95000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>525000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>141000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>708000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>516000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>717000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>547000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>544000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>243000</v>
       </c>
     </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1889,150 +1937,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>703000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1042000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1681000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>284000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1055000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>215000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>101000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1518000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-285000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>519000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3134000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>35000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1512000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>424000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>44000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>716000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1475000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2960000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>3461000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2722000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2429000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>3776000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1815000</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>322000</v>
+      </c>
+      <c r="E27" s="3">
         <v>58000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>700000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>177000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>230000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>33000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>391000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>21000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>60000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>656000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>189000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>40000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>79000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-355000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>386000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>553000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1322000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1081000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>761000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>778000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1198000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>607000</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2102,8 +2159,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2173,8 +2233,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2244,8 +2307,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2315,53 +2381,56 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>310000</v>
+      </c>
+      <c r="E32" s="3">
         <v>217000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>763000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-363000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>902000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-435000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>217000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-433000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-315000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-284000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-102000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>819000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-123000</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
@@ -2386,79 +2455,85 @@
       <c r="Y32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>364000</v>
+      </c>
+      <c r="E33" s="3">
         <v>102000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>743000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>219000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>272000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>73000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>432000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>64000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>43000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>102000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>699000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>230000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>81000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>120000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-355000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>386000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>553000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1322000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1081000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>761000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>778000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1198000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>607000</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2528,155 +2603,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>364000</v>
+      </c>
+      <c r="E35" s="3">
         <v>102000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>743000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>219000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>272000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>73000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>432000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>64000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>43000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>102000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>699000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>230000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>81000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>120000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-355000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>386000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>553000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1322000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1081000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>761000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>778000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1198000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>607000</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2702,8 +2786,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2729,79 +2814,83 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>14885000</v>
+      </c>
+      <c r="E41" s="3">
         <v>15030000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>16242000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>16682000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>13703000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>12437000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>15051000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>11824000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>11249000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>11742000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>11222000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>12087000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>12427000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>13049000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>14396000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>11306000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>12205000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>11816000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>12694000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>11343000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>10459000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>9826000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>9933000</v>
       </c>
     </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2812,11 +2901,11 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>8709000</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
         <v>0</v>
       </c>
@@ -2871,195 +2960,204 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>33883000</v>
+      </c>
+      <c r="E43" s="3">
         <v>32795000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>25727000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>22171000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>31551000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>28435000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>22635000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>30294000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>30275000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>30560000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>24783000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>30718000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>29152000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>27925000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>27378000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>29813000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>26563000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>25587000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>21760000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>20272000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>19543000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>20202000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>18928000</v>
       </c>
     </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>7227000</v>
+      </c>
+      <c r="E44" s="3">
         <v>6520000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>8849000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>6049000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>6014000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5506000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>8458000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>6347000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>7375000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>6929000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>11412000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>8049000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>8955000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>8885000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>12843000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>12138000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>12870000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>12003000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>11415000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>11620000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>11187000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>10346000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>10360000</v>
       </c>
     </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>15394000</v>
+      </c>
+      <c r="E45" s="3">
         <v>10081000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>12780000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>13896000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>19716000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>13567000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>10291000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>7282000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4129000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3583000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2489000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3041000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2684000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2423000</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -3084,53 +3182,56 @@
       <c r="Y45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>71389000</v>
+      </c>
+      <c r="E46" s="3">
         <v>64426000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>80331000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>67507000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>70984000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>59945000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>72160000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>55747000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>53028000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>52814000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>63539000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>53895000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>53218000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>52282000</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -3155,221 +3256,233 @@
       <c r="Y46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>109715000</v>
+      </c>
+      <c r="E47" s="3">
         <v>102809000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>100963000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>95928000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>92661000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>91961000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>86055000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>85373000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>82570000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>76571000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>77544000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>71957000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>73185000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>71703000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>73993000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>67302000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>68350000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>62818000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>62646000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>60913000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>62331000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>61546000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>59057000</v>
       </c>
     </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>249162000</v>
+      </c>
+      <c r="E48" s="3">
         <v>253992000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>251605000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>249615000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>246550000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>248868000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>256684000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>277891000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>273363000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>273192000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>271769000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>257948000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>247242000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>243937000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>239368000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>223141000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>221171000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>222715000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>216354000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>211254000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>199096000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>195538000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>196791000</v>
       </c>
     </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>79084000</v>
+      </c>
+      <c r="E49" s="3">
         <v>81146000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>81851000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>83981000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>78610000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>74243000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>71802000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>72232000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>71442000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>72814000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>73905000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>74500000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>73546000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>73251000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>67073000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>63188000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>56854000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>52713000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>50836000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>43055000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>39971000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>38923000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>39372000</v>
       </c>
     </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3439,8 +3552,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3510,79 +3626,85 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2204000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2480000</v>
       </c>
-      <c r="E52" s="3" t="s">
+      <c r="F52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3112000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3245000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3200000</v>
       </c>
-      <c r="I52" s="3" t="s">
+      <c r="J52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4684000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4466000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4358000</v>
       </c>
-      <c r="M52" s="3" t="s">
+      <c r="N52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4136000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4051000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4038000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6233000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>12262000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>13853000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>14301000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>15298000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>6967000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>6630000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>8642000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>9255000</v>
       </c>
     </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3652,79 +3774,85 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>525515000</v>
+      </c>
+      <c r="E54" s="3">
         <v>519613000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>518971000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>514586000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>506068000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>491577000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>490424000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>508144000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>497314000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>491855000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>490095000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>475815000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>463134000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>456742000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>441284000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>419150000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>411866000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>401953000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>391003000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>365424000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>349217000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>345023000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>343696000</v>
       </c>
     </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3750,8 +3878,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3777,195 +3906,202 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>32903000</v>
+      </c>
+      <c r="E57" s="3">
         <v>33569000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>16252000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>30633000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>30514000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>27904000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>13202000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>32200000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>32445000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>31756000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>13470000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>32214000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>34908000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>34709000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>57065000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>52859000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>51134000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>53810000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>52546000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>52087000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>50330000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>48862000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>50682000</v>
       </c>
     </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>28400000</v>
+      </c>
+      <c r="E58" s="3">
         <v>34238000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>41353000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2098000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2528000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1739000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>39165000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2000000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2455000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1537000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>59306000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1636000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1634000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>973000</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
         <v>683000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1315000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>356000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>31879000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>350000</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
-      </c>
       <c r="X58" s="3">
         <v>0</v>
       </c>
       <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="3">
         <v>21287000</v>
       </c>
     </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>9218000</v>
+      </c>
+      <c r="E59" s="3">
         <v>4410000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5891000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5484000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>9423000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5993000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4721000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2516000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>538000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>410000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>118000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1492000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1489000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>680000</v>
       </c>
-      <c r="Q59" s="3">
-        <v>0</v>
-      </c>
       <c r="R59" s="3">
         <v>0</v>
       </c>
@@ -3990,53 +4126,56 @@
       <c r="Y59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>70521000</v>
+      </c>
+      <c r="E60" s="3">
         <v>72217000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>63496000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>38215000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>42465000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>35636000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>57088000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>36716000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>35438000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>33703000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>72894000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>35342000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>38031000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>36362000</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -4061,150 +4200,159 @@
       <c r="Y60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>240513000</v>
+      </c>
+      <c r="E61" s="3">
         <v>233229000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>231268000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>260874000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>251501000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>247479000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>210048000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>250305000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>245082000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>238976000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>187168000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>224930000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>218069000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>221854000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>214074000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>203793000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>198324000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>184678000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>144053000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>166124000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>152271000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>148589000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>127114000</v>
       </c>
     </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>21585000</v>
+      </c>
+      <c r="E62" s="3">
         <v>21699000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>31004000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>26131000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>25995000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>24898000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>32638000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>26358000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>24810000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>25474000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>36804000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>27630000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>27118000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>27469000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>24066000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>23515000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>22293000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>22044000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>23476000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>19502000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>17201000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>17991000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>18272000</v>
       </c>
     </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4274,8 +4422,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4345,8 +4496,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4416,79 +4570,85 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>358879000</v>
+      </c>
+      <c r="E66" s="3">
         <v>353971000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>352777000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>351506000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>344423000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>332647000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>325041000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>338245000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>329750000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>322825000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>321853000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>312558000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>307551000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>309828000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>397531000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>374604000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>366069000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>354409000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>344648000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>322471000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>311703000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>307925000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>307858000</v>
       </c>
     </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4514,8 +4674,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4585,8 +4746,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4656,19 +4820,22 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>4090000</v>
+        <v>4088000</v>
       </c>
       <c r="E70" s="3">
         <v>4090000</v>
       </c>
       <c r="F70" s="3">
-        <v>4103000</v>
+        <v>4090000</v>
       </c>
       <c r="G70" s="3">
         <v>4103000</v>
@@ -4701,7 +4868,7 @@
         <v>4103000</v>
       </c>
       <c r="Q70" s="3">
-        <v>4145000</v>
+        <v>4103000</v>
       </c>
       <c r="R70" s="3">
         <v>4145000</v>
@@ -4727,8 +4894,11 @@
       <c r="Y70" s="3">
         <v>4145000</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>4145000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4798,79 +4968,85 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>16210000</v>
+      </c>
+      <c r="E72" s="3">
         <v>16161000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>16665000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>16203000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>16248000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>16450000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>17066000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>16931000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>17131000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>17508000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>18006000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>17543000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>17646000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>17747000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>18904000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>18585000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>19378000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>20032000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>19115000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>17788000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>17180000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>17022000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>15952000</v>
       </c>
     </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4940,8 +5116,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5011,8 +5190,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5082,79 +5264,85 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>42483000</v>
+      </c>
+      <c r="E76" s="3">
         <v>42697000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>43796000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>42554000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>42493000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>41160000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>41874000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>42368000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>41232000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>40477000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>41674000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>40368000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>40498000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>39960000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>39608000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>40401000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>41652000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>43399000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>42210000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>38808000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>33369000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>32953000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>31693000</v>
       </c>
     </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5224,155 +5412,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>364000</v>
+      </c>
+      <c r="E81" s="3">
         <v>102000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>743000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>219000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>272000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>73000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>432000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>64000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>43000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>102000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>699000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>230000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>81000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>120000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-355000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>386000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>553000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1322000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1081000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>761000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>778000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1198000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>607000</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5398,79 +5595,83 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2534000</v>
+      </c>
+      <c r="E83" s="3">
         <v>2455000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2417000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2410000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2435000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2475000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2427000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2246000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2214000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2188000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1989000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1997000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1886000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1811000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1989000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1997000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1886000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1811000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1739000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1617000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1571000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1510000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1536000</v>
       </c>
     </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5540,8 +5741,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5611,8 +5815,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5682,8 +5889,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5753,8 +5963,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5824,79 +6037,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1865000</v>
+      </c>
+      <c r="E89" s="3">
         <v>225000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4245000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3008000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2011000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1694000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3165000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3388000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>698000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>318000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1506000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3437000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>406000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1118000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3125000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2186000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3114000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>484000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2276000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2055000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1551000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1785000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>2843000</v>
       </c>
     </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5922,79 +6141,83 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3671000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-5904000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-5243000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3938000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2756000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2815000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3161000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2725000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2385000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2901000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2708000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2158000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1651000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1552000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4322000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4895000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4604000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3079000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-6029000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-4710000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1259000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1680000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1138000</v>
       </c>
     </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6064,8 +6287,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6135,79 +6361,85 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-10907000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5996000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-6530000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-8014000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-5909000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-11324000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-9433000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-7329000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-8329000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4873000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5724000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-9874000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-862000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-13302000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-7408000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-14023000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-15547000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2672000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-12226000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-5930000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>1270000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-4159000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1121000</v>
       </c>
     </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6233,8 +6465,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6242,7 +6475,7 @@
         <v>160000</v>
       </c>
       <c r="E96" s="3">
-        <v>138000</v>
+        <v>160000</v>
       </c>
       <c r="F96" s="3">
         <v>138000</v>
@@ -6254,10 +6487,10 @@
         <v>138000</v>
       </c>
       <c r="I96" s="3">
+        <v>138000</v>
+      </c>
+      <c r="J96" s="3">
         <v>123000</v>
-      </c>
-      <c r="J96" s="3">
-        <v>124000</v>
       </c>
       <c r="K96" s="3">
         <v>124000</v>
@@ -6266,46 +6499,49 @@
         <v>124000</v>
       </c>
       <c r="M96" s="3">
+        <v>124000</v>
+      </c>
+      <c r="N96" s="3">
         <v>107000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>109000</v>
-      </c>
-      <c r="O96" s="3">
-        <v>110000</v>
       </c>
       <c r="P96" s="3">
         <v>110000</v>
       </c>
       <c r="Q96" s="3">
+        <v>110000</v>
+      </c>
+      <c r="R96" s="3">
         <v>-260000</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-256000</v>
       </c>
       <c r="S96" s="3">
         <v>-256000</v>
       </c>
       <c r="T96" s="3">
+        <v>-256000</v>
+      </c>
+      <c r="U96" s="3">
         <v>-257000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-241000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-240000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-772000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-233000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-217000</v>
       </c>
     </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6375,8 +6611,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6446,8 +6685,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6517,217 +6759,229 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>9673000</v>
+      </c>
+      <c r="E100" s="3">
         <v>4483000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1973000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>7825000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>5117000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>6772000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>9832000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>4490000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>7369000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>5209000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>3133000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>6256000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-228000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>10766000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>7100000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>11103000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>13104000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1153000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>11321000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>4859000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-2306000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>2387000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-706000</v>
       </c>
     </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>56000</v>
+      </c>
+      <c r="E101" s="3">
         <v>235000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-269000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>108000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-187000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-113000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>189000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-171000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>108000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>79000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>273000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-165000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-282000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>157000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>273000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-165000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-282000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>157000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-20000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-100000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>118000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-120000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>194000</v>
       </c>
     </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>680000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1244000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-425000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2893000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1275000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2623000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3295000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>657000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-449000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>541000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-896000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-352000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-576000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1339000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>3090000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-899000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>389000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-878000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1351000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>884000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>633000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-107000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1210000</v>
       </c>
     </row>
